--- a/output/stock_quant_scores/LLY_info.xlsx
+++ b/output/stock_quant_scores/LLY_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FV2"/>
+  <dimension ref="A1:FZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,215 +1101,235 @@
       </c>
       <c r="EF1" s="1" t="inlineStr">
         <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1435,34 +1455,34 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>746.98</v>
+        <v>714.59</v>
       </c>
       <c r="AD2" t="n">
-        <v>745.99</v>
+        <v>724.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>736.16</v>
+        <v>717.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>746.5525</v>
+        <v>728.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>746.98</v>
+        <v>714.59</v>
       </c>
       <c r="AH2" t="n">
-        <v>745.99</v>
+        <v>724.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>736.16</v>
+        <v>717.13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>746.5525</v>
+        <v>728.98</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AM2" t="n">
         <v>1755216000</v>
@@ -1477,46 +1497,46 @@
         <v>0.465</v>
       </c>
       <c r="AQ2" t="n">
-        <v>48.254738</v>
+        <v>47.386524</v>
       </c>
       <c r="AR2" t="n">
-        <v>32.602825</v>
+        <v>31.974403</v>
       </c>
       <c r="AS2" t="n">
-        <v>1274405</v>
+        <v>3555517</v>
       </c>
       <c r="AT2" t="n">
-        <v>1274405</v>
+        <v>3555517</v>
       </c>
       <c r="AU2" t="n">
-        <v>4415996</v>
+        <v>4426836</v>
       </c>
       <c r="AV2" t="n">
-        <v>3326440</v>
+        <v>3733050</v>
       </c>
       <c r="AW2" t="n">
-        <v>3326440</v>
+        <v>3733050</v>
       </c>
       <c r="AX2" t="n">
-        <v>738.51</v>
+        <v>722.08</v>
       </c>
       <c r="AY2" t="n">
-        <v>738.99</v>
+        <v>724.49</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>662284337152</v>
+        <v>649518776320</v>
       </c>
       <c r="BC2" t="n">
         <v>623.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>939.3</v>
+        <v>937</v>
       </c>
       <c r="BE2" t="n">
         <v>972.53</v>
@@ -1525,19 +1545,19 @@
         <v>2.039063</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.435372</v>
+        <v>12.195681</v>
       </c>
       <c r="BH2" t="n">
-        <v>737.9878</v>
+        <v>735.1464</v>
       </c>
       <c r="BI2" t="n">
-        <v>785.3759</v>
+        <v>783.86993</v>
       </c>
       <c r="BJ2" t="n">
         <v>5.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0074968543</v>
+        <v>0.007836661</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1548,43 +1568,43 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>707101786112</v>
+        <v>686956609536</v>
       </c>
       <c r="BO2" t="n">
         <v>0.25911</v>
       </c>
       <c r="BP2" t="n">
-        <v>895419493</v>
+        <v>895437448</v>
       </c>
       <c r="BQ2" t="n">
         <v>896456759</v>
       </c>
       <c r="BR2" t="n">
-        <v>8041246</v>
+        <v>7323001</v>
       </c>
       <c r="BS2" t="n">
-        <v>7172654</v>
+        <v>8696819</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="BW2" t="n">
         <v>0.00164</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.83844</v>
+        <v>0.83841</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0101</v>
+        <v>0.0092</v>
       </c>
       <c r="CA2" t="n">
         <v>906021621</v>
@@ -1593,7 +1613,7 @@
         <v>20.375</v>
       </c>
       <c r="CC2" t="n">
-        <v>36.259144</v>
+        <v>35.560246</v>
       </c>
       <c r="CD2" t="n">
         <v>1735603200</v>
@@ -1611,7 +1631,7 @@
         <v>13799900160</v>
       </c>
       <c r="CI2" t="n">
-        <v>15.31</v>
+        <v>15.29</v>
       </c>
       <c r="CJ2" t="n">
         <v>22.66</v>
@@ -1625,16 +1645,16 @@
         <v>876960000</v>
       </c>
       <c r="CM2" t="n">
-        <v>13.277</v>
+        <v>12.899</v>
       </c>
       <c r="CN2" t="n">
-        <v>28.541</v>
+        <v>27.728</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.19206977</v>
+        <v>-0.18217939</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CQ2" t="n">
         <v>1.5</v>
@@ -1648,7 +1668,7 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>738.78</v>
+        <v>724.54</v>
       </c>
       <c r="CU2" t="n">
         <v>1190</v>
@@ -1757,7 +1777,7 @@
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>Nasdaq Real Time Price</t>
+          <t>Delayed Quote</t>
         </is>
       </c>
       <c r="EA2" t="b">
@@ -1784,153 +1804,165 @@
         </is>
       </c>
       <c r="EF2" t="n">
-        <v>1758740026</v>
+        <v>1758931162</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.7922363</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.0010735088</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-46.595886</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-0.059329405</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
+        <v>1758916802</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>NYQ</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>finmb_285467</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-14400000</v>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>1.8 - Buy</t>
+          <t>us_market</t>
         </is>
       </c>
       <c r="EN2" t="b">
         <v>0</v>
       </c>
-      <c r="EO2" t="n">
-        <v>-1.0977471</v>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="EP2" t="n">
-        <v>-8.199951</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>736.16 - 746.5525</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
+        <v>1.3924</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>724.54</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.33945298</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>722.0805</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-2.4594727</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>9.949949999999999</v>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>717.13 - 728.98</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="ES2" t="n">
-        <v>4415996</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>115</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>0.18435986</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>623.78 - 939.3</t>
-        </is>
-      </c>
-      <c r="EW2" t="n">
-        <v>-200.51996</v>
-      </c>
       <c r="EX2" t="n">
-        <v>-0.21347807</v>
+        <v>4426836</v>
       </c>
       <c r="EY2" t="n">
-        <v>-19.206978</v>
+        <v>100.75995</v>
       </c>
       <c r="EZ2" t="n">
+        <v>0.16153122</v>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>623.78 - 937.0</t>
+        </is>
+      </c>
+      <c r="FB2" t="n">
+        <v>-212.46002</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>-0.22674495</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>-18.21794</v>
+      </c>
+      <c r="FE2" t="n">
         <v>1757462400</v>
       </c>
-      <c r="FA2" t="n">
+      <c r="FF2" t="n">
         <v>1761827400</v>
       </c>
-      <c r="FB2" t="n">
+      <c r="FG2" t="n">
         <v>1761827400</v>
       </c>
-      <c r="FC2" t="n">
+      <c r="FH2" t="n">
         <v>1761827400</v>
       </c>
-      <c r="FD2" t="n">
+      <c r="FI2" t="n">
         <v>1761832800</v>
       </c>
-      <c r="FE2" t="n">
+      <c r="FJ2" t="n">
         <v>1761832800</v>
       </c>
-      <c r="FF2" t="b">
+      <c r="FK2" t="b">
         <v>0</v>
       </c>
-      <c r="FG2" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="FH2" t="n">
+      <c r="FL2" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="FM2" t="n">
         <v>22.66</v>
       </c>
-      <c r="FI2" t="n">
+      <c r="FN2" t="n">
         <v>22.84465</v>
       </c>
-      <c r="FJ2" t="n">
-        <v>32.339302</v>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FL2" t="b">
+      <c r="FO2" t="n">
+        <v>31.715958</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>-10.606445</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>-0.014427664</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>-59.329956</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>-0.07568852</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV2" t="inlineStr">
+        <is>
+          <t>1.8 - Buy</t>
+        </is>
+      </c>
+      <c r="FW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FX2" t="b">
         <v>1</v>
       </c>
-      <c r="FM2" t="n">
+      <c r="FY2" t="n">
         <v>76253400000</v>
       </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>NYQ</t>
-        </is>
-      </c>
-      <c r="FO2" t="inlineStr">
-        <is>
-          <t>finmb_285467</t>
-        </is>
-      </c>
-      <c r="FP2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="FQ2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="FR2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="FS2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="FT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FU2" t="n">
-        <v>738.78</v>
-      </c>
-      <c r="FV2" t="n">
-        <v>0.8177</v>
+      <c r="FZ2" t="n">
+        <v>0.7931</v>
       </c>
     </row>
   </sheetData>
